--- a/Submission/Tables.xlsx
+++ b/Submission/Tables.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" state="visible" r:id="rId3"/>
@@ -13,6 +13,7 @@
     <sheet name="Table 3" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Table 4" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Table 5" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Table 6" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -24,9 +25,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="179">
-  <si>
-    <t xml:space="preserve">Table 1: Summary univariate statistics of selected geochemical and colour soil properties for each site (n = 49). Geochemical concentrations are reported in ppm, excecpt Ca and Fe (%).</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="216">
+  <si>
+    <t xml:space="preserve">Table 1: Summary univariate statistics of selected geochemical and colour soil properties for each site (n = 49). Geochemical concentrations are reported in ppm, except Ca and Fe (%).</t>
   </si>
   <si>
     <t xml:space="preserve">Property</t>
@@ -535,6 +536,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">§</t>
     </r>
@@ -567,6 +569,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -576,6 +579,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">(CI</t>
     </r>
@@ -586,6 +590,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">95%</t>
     </r>
@@ -595,6 +600,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">)</t>
     </r>
@@ -643,42 +649,10 @@
     <t xml:space="preserve">0.38 (0.22, 0.56)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">&lt;0.01</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (0, 0.31)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">&lt;0.01</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (0, 0.01)</t>
-    </r>
+    <t xml:space="preserve">&lt;0.01 (0, 0.31)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;0.01 (0, 0.01)</t>
   </si>
   <si>
     <t xml:space="preserve">0.70 (0.48, 0.88)</t>
@@ -720,45 +694,10 @@
     <t xml:space="preserve">0.03 (0, 0.42)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">&lt;0.01 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(0, 0)</t>
-    </r>
+    <t xml:space="preserve">&lt;0.01 (0, 0)</t>
   </si>
   <si>
     <t xml:space="preserve">0.31 (0.02, 0.67)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">&lt;0.01</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (0, 0)</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">0.25 (0.01, 0.65)</t>
@@ -868,6 +807,120 @@
   <si>
     <t xml:space="preserve">** Mean square error and 95% Confidence Intervals</t>
   </si>
+  <si>
+    <t xml:space="preserve">Table 6. Mean (standard deviation) of terrain attributes for each cluster at the agricultural and forested sites.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terrain attribute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agricultural Site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">310.0 (0.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 309.2 (0.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5 (0.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 10.6 (0.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relative Slope Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8 (0.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.2 (0.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vertical distance to channel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1 (0.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.0 (0.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catchment area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.3 (728.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1183.9 (1983.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0 (0.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -0.0 (0.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0 (0.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forest Site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369.4 (2.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 369.9 (3.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 367.1 (4.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7 (0.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5.5 (0.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5.2 (0.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1 (0.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.4 (0.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.1 (0.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.7 (0.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.5 (0.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">252.3 (425.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 147.1 (520.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2571.6 (4255.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;0.01 (&lt;0.01)</t>
+  </si>
 </sst>
 </file>
 
@@ -878,7 +931,7 @@
     <numFmt numFmtId="165" formatCode="0.00"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="12">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -945,7 +998,6 @@
     </font>
     <font>
       <b val="true"/>
-      <vertAlign val="superscript"/>
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -953,20 +1005,9 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <vertAlign val="subscript"/>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1032,7 +1073,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="40">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1157,16 +1198,8 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1177,28 +1210,28 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1221,37 +1254,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -1325,7 +1358,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G34"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.87"/>
   </cols>
@@ -2098,7 +2131,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.08"/>
   </cols>
@@ -2503,7 +2536,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
@@ -3252,7 +3285,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H29"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
@@ -3975,11 +4008,11 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G33"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="2.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="24.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="2.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="24.62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4048,19 +4081,19 @@
       <c r="C5" s="6" t="n">
         <v>0.43</v>
       </c>
-      <c r="D5" s="31" t="n">
+      <c r="D5" s="7" t="n">
         <v>0.98</v>
       </c>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31" t="s">
+      <c r="E5" s="7"/>
+      <c r="F5" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="G5" s="31" t="s">
+      <c r="G5" s="7" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="31" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="15" t="n">
@@ -4069,19 +4102,19 @@
       <c r="C6" s="8" t="n">
         <v>0.01</v>
       </c>
-      <c r="D6" s="31" t="n">
+      <c r="D6" s="7" t="n">
         <v>0.99</v>
       </c>
-      <c r="E6" s="31"/>
-      <c r="F6" s="31" t="s">
+      <c r="E6" s="7"/>
+      <c r="F6" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="G6" s="31" t="s">
+      <c r="G6" s="7" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="31" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="15" t="n">
@@ -4090,19 +4123,19 @@
       <c r="C7" s="8" t="n">
         <v>0.01</v>
       </c>
-      <c r="D7" s="31" t="n">
+      <c r="D7" s="7" t="n">
         <v>0.99</v>
       </c>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31" t="s">
+      <c r="E7" s="7"/>
+      <c r="F7" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="G7" s="31" t="s">
+      <c r="G7" s="7" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="32" t="s">
+      <c r="A8" s="31" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="15" t="s">
@@ -4111,19 +4144,19 @@
       <c r="C8" s="8" t="n">
         <v>1.86</v>
       </c>
-      <c r="D8" s="31" t="n">
+      <c r="D8" s="7" t="n">
         <v>0.85</v>
       </c>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31" t="s">
+      <c r="E8" s="7"/>
+      <c r="F8" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="G8" s="31" t="s">
+      <c r="G8" s="7" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="31" t="s">
         <v>15</v>
       </c>
       <c r="B9" s="15" t="n">
@@ -4132,19 +4165,19 @@
       <c r="C9" s="8" t="n">
         <v>0.39</v>
       </c>
-      <c r="D9" s="31" t="n">
+      <c r="D9" s="7" t="n">
         <v>0.99</v>
       </c>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31" t="s">
+      <c r="E9" s="7"/>
+      <c r="F9" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="G9" s="31" t="s">
+      <c r="G9" s="7" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="31" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="15" t="n">
@@ -4153,19 +4186,19 @@
       <c r="C10" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="31" t="n">
+      <c r="D10" s="7" t="n">
         <v>0.95</v>
       </c>
-      <c r="E10" s="31"/>
-      <c r="F10" s="33" t="s">
+      <c r="E10" s="7"/>
+      <c r="F10" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="G10" s="33" t="s">
+      <c r="G10" s="7" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="32" t="s">
+      <c r="A11" s="31" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="15" t="n">
@@ -4174,19 +4207,19 @@
       <c r="C11" s="8" t="n">
         <v>1.89</v>
       </c>
-      <c r="D11" s="31" t="n">
+      <c r="D11" s="7" t="n">
         <v>0.99</v>
       </c>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31" t="s">
+      <c r="E11" s="7"/>
+      <c r="F11" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="G11" s="31" t="s">
+      <c r="G11" s="7" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="32" t="s">
+      <c r="A12" s="31" t="s">
         <v>19</v>
       </c>
       <c r="B12" s="15" t="n">
@@ -4195,19 +4228,19 @@
       <c r="C12" s="8" t="n">
         <v>3.75</v>
       </c>
-      <c r="D12" s="31" t="n">
+      <c r="D12" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31" t="s">
+      <c r="E12" s="7"/>
+      <c r="F12" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="G12" s="31" t="s">
+      <c r="G12" s="7" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="31" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="15" t="n">
@@ -4216,19 +4249,19 @@
       <c r="C13" s="8" t="n">
         <v>441.33</v>
       </c>
-      <c r="D13" s="31" t="n">
+      <c r="D13" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="31"/>
-      <c r="F13" s="31" t="s">
+      <c r="E13" s="7"/>
+      <c r="F13" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="G13" s="31" t="s">
+      <c r="G13" s="7" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="34" t="s">
+      <c r="A14" s="32" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="15" t="n">
@@ -4237,19 +4270,19 @@
       <c r="C14" s="8" t="n">
         <v>0.03</v>
       </c>
-      <c r="D14" s="31" t="n">
+      <c r="D14" s="7" t="n">
         <v>0.97</v>
       </c>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31" t="s">
+      <c r="E14" s="7"/>
+      <c r="F14" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="G14" s="31" t="s">
+      <c r="G14" s="7" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="34" t="s">
+      <c r="A15" s="32" t="s">
         <v>23</v>
       </c>
       <c r="B15" s="15" t="n">
@@ -4258,19 +4291,19 @@
       <c r="C15" s="8" t="n">
         <v>0.53</v>
       </c>
-      <c r="D15" s="31" t="n">
+      <c r="D15" s="7" t="n">
         <v>0.9</v>
       </c>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31" t="s">
+      <c r="E15" s="7"/>
+      <c r="F15" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G15" s="31" t="s">
+      <c r="G15" s="7" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="34" t="s">
+      <c r="A16" s="32" t="s">
         <v>25</v>
       </c>
       <c r="B16" s="15" t="n">
@@ -4279,19 +4312,19 @@
       <c r="C16" s="8" t="n">
         <v>0.64</v>
       </c>
-      <c r="D16" s="31" t="n">
+      <c r="D16" s="7" t="n">
         <v>0.93</v>
       </c>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31" t="s">
+      <c r="E16" s="7"/>
+      <c r="F16" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="G16" s="31" t="s">
+      <c r="G16" s="7" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="34" t="s">
+      <c r="A17" s="32" t="s">
         <v>27</v>
       </c>
       <c r="B17" s="15" t="n">
@@ -4300,19 +4333,19 @@
       <c r="C17" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="31" t="n">
+      <c r="D17" s="7" t="n">
         <v>0.94</v>
       </c>
-      <c r="E17" s="31"/>
-      <c r="F17" s="31" t="s">
+      <c r="E17" s="7"/>
+      <c r="F17" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="G17" s="33" t="s">
+      <c r="G17" s="7" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="35" t="s">
+      <c r="A18" s="33" t="s">
         <v>28</v>
       </c>
       <c r="B18" s="23" t="n">
@@ -4321,15 +4354,15 @@
       <c r="C18" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="31" t="n">
+      <c r="D18" s="7" t="n">
         <v>0.96</v>
       </c>
-      <c r="E18" s="31"/>
-      <c r="F18" s="31" t="s">
+      <c r="E18" s="7"/>
+      <c r="F18" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="G18" s="33" t="s">
-        <v>151</v>
+      <c r="G18" s="7" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4353,103 +4386,103 @@
       <c r="C20" s="6" t="n">
         <v>0.32</v>
       </c>
-      <c r="D20" s="31" t="n">
+      <c r="D20" s="7" t="n">
         <v>0.98</v>
       </c>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31" t="s">
+      <c r="E20" s="7"/>
+      <c r="F20" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G20" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="G20" s="31" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" s="15" t="s">
         <v>153</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" s="15" t="s">
-        <v>154</v>
       </c>
       <c r="C21" s="8" t="n">
         <v>0.97</v>
       </c>
-      <c r="D21" s="31" t="n">
+      <c r="D21" s="7" t="n">
         <v>0.93</v>
       </c>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31" t="s">
+      <c r="E21" s="7"/>
+      <c r="F21" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="G21" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="G21" s="31" t="s">
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="15" t="s">
         <v>156</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>157</v>
       </c>
       <c r="C22" s="8" t="n">
         <v>0.01</v>
       </c>
-      <c r="D22" s="31" t="n">
+      <c r="D22" s="7" t="n">
         <v>0.9</v>
       </c>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31" t="s">
+      <c r="E22" s="7"/>
+      <c r="F22" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="G22" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="G22" s="31" t="s">
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="15" t="s">
         <v>159</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="B23" s="15" t="s">
-        <v>160</v>
       </c>
       <c r="C23" s="8" t="n">
         <v>0.55</v>
       </c>
-      <c r="D23" s="31" t="n">
+      <c r="D23" s="7" t="n">
         <v>0.61</v>
       </c>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31" t="s">
+      <c r="E23" s="7"/>
+      <c r="F23" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="G23" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="G23" s="31" t="s">
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="15" t="s">
         <v>162</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" s="15" t="s">
-        <v>163</v>
       </c>
       <c r="C24" s="8" t="n">
         <v>2.49</v>
       </c>
-      <c r="D24" s="31" t="n">
+      <c r="D24" s="7" t="n">
         <v>0.88</v>
       </c>
-      <c r="E24" s="31"/>
-      <c r="F24" s="31" t="s">
+      <c r="E24" s="7"/>
+      <c r="F24" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="G24" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="G24" s="31" t="s">
-        <v>165</v>
-      </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="32" t="s">
+      <c r="A25" s="31" t="s">
         <v>17</v>
       </c>
       <c r="B25" s="15" t="n">
@@ -4458,40 +4491,40 @@
       <c r="C25" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D25" s="31" t="n">
+      <c r="D25" s="7" t="n">
         <v>0.89</v>
       </c>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31" t="s">
+      <c r="E25" s="7"/>
+      <c r="F25" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" s="15" t="s">
         <v>166</v>
-      </c>
-      <c r="G25" s="33" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="B26" s="15" t="s">
-        <v>167</v>
       </c>
       <c r="C26" s="8" t="n">
         <v>7.78</v>
       </c>
-      <c r="D26" s="31" t="n">
+      <c r="D26" s="7" t="n">
         <v>0.76</v>
       </c>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31" t="s">
+      <c r="E26" s="7"/>
+      <c r="F26" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="G26" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="G26" s="31" t="s">
-        <v>169</v>
-      </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="32" t="s">
+      <c r="A27" s="31" t="s">
         <v>20</v>
       </c>
       <c r="B27" s="15" t="n">
@@ -4500,52 +4533,52 @@
       <c r="C27" s="8" t="n">
         <v>44.47</v>
       </c>
-      <c r="D27" s="31" t="n">
+      <c r="D27" s="7" t="n">
         <v>0.98</v>
       </c>
-      <c r="E27" s="31"/>
-      <c r="F27" s="31" t="s">
+      <c r="E27" s="7"/>
+      <c r="F27" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="G27" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="G27" s="31" t="s">
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="23" t="s">
         <v>171</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" s="23" t="s">
-        <v>172</v>
       </c>
       <c r="C28" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="36" t="n">
+      <c r="D28" s="9" t="n">
         <v>0.75</v>
       </c>
-      <c r="E28" s="36"/>
-      <c r="F28" s="36" t="s">
+      <c r="E28" s="9"/>
+      <c r="F28" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="34" t="s">
         <v>173</v>
       </c>
-      <c r="G28" s="37" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="38" t="s">
-        <v>174</v>
-      </c>
-      <c r="B29" s="38"/>
-      <c r="C29" s="38"/>
-      <c r="D29" s="38"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="38"/>
-      <c r="G29" s="38"/>
+      <c r="B29" s="34"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="34"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="24" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B30" s="24"/>
       <c r="C30" s="24"/>
@@ -4555,37 +4588,37 @@
       <c r="G30" s="24"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="39" t="s">
+      <c r="A31" s="35" t="s">
+        <v>175</v>
+      </c>
+      <c r="B31" s="35"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="35"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="24" t="s">
         <v>176</v>
       </c>
-      <c r="B31" s="39"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="39"/>
-      <c r="G31" s="39"/>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="40" t="s">
+      <c r="B32" s="24"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="34" t="s">
         <v>177</v>
       </c>
-      <c r="B32" s="40"/>
-      <c r="C32" s="40"/>
-      <c r="D32" s="40"/>
-      <c r="E32" s="40"/>
-      <c r="F32" s="40"/>
-      <c r="G32" s="40"/>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="41" t="s">
-        <v>178</v>
-      </c>
-      <c r="B33" s="41"/>
-      <c r="C33" s="41"/>
-      <c r="D33" s="41"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="41"/>
+      <c r="B33" s="34"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
+      <c r="G33" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -4609,4 +4642,246 @@
     <oddFooter>&amp;CPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="14.66"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="36" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2" s="37" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="38" t="s">
+        <v>183</v>
+      </c>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>184</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>186</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>188</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>195</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>197</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="39" t="s">
+        <v>199</v>
+      </c>
+      <c r="C10" s="39" t="s">
+        <v>198</v>
+      </c>
+      <c r="D10" s="39"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="38" t="s">
+        <v>200</v>
+      </c>
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>201</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>204</v>
+      </c>
+      <c r="C14" s="0" t="s">
+        <v>205</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>188</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="C15" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="D15" s="0" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="C16" s="0" t="s">
+        <v>210</v>
+      </c>
+      <c r="D16" s="0" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>194</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>212</v>
+      </c>
+      <c r="C17" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="D17" s="0" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="C19" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="D19" s="39" t="s">
+        <v>215</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A12:D12"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>